--- a/addon_ugears/ug_base_distrib/static/xls/template_budget_distrib.xlsx
+++ b/addon_ugears/ug_base_distrib/static/xls/template_budget_distrib.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="25170" windowHeight="11250"/>
   </bookViews>
   <sheets>
-    <sheet name="Distr Incomes" sheetId="1" r:id="rId1"/>
+    <sheet name="Distr Budget" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
